--- a/outputs/Block5B_Senate_State_Model_Diagnostics.xlsx
+++ b/outputs/Block5B_Senate_State_Model_Diagnostics.xlsx
@@ -432,7 +432,7 @@
         <v>5.576424735558597</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -443,13 +443,13 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>5.030461973215973</v>
+        <v>5.335678432032632</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>5.116327771031301</v>
+        <v>5.392670902908676</v>
       </c>
       <c r="C4">
         <v>1</v>
